--- a/wildlife/reports/United-Kingdom/trend/Abingdon/Flora/Cornflower.xlsx
+++ b/wildlife/reports/United-Kingdom/trend/Abingdon/Flora/Cornflower.xlsx
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
